--- a/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9519,6 +9519,272 @@
       </c>
       <c r="AE72" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BW-2026-076</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BW260025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Lisa Czajko</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>47×37×34cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0.059 CBM</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>11</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>478080</v>
+      </c>
+      <c r="U73" t="n">
+        <v>285000</v>
+      </c>
+      <c r="V73" t="n">
+        <v>193080</v>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>5 Toms way LaGrangeville NY 12540</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>1-347-739-2112</t>
+        </is>
+      </c>
+      <c r="AC73" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>10.52</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BW-2026-077</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BW260026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Jayde Lysne</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>21×33×14cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0.010 CBM</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>79680</v>
+      </c>
+      <c r="U74" t="n">
+        <v>60000</v>
+      </c>
+      <c r="V74" t="n">
+        <v>19680</v>
+      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>9 McDougall Dr Lincoln, ND 58504 USA</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>+17017718847</t>
+        </is>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -9532,7 +9798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9866,6 +10132,58 @@
           <t>미지급</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>회식비</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>135900</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10203,7 +10521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
@@ -10157,7 +10157,11 @@
           <t>회식비</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10183,7 +10187,11 @@
           <t>1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10521,7 +10529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
@@ -8633,7 +8633,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>위해신노통관사</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8691,7 +8691,11 @@
       <c r="V66" t="n">
         <v>4425000</v>
       </c>
-      <c r="W66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>인천시노 1톤차량 운임 50000원 비용지불</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr">
         <is>
           <t>이상복</t>

--- a/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-23.xlsx
@@ -3377,7 +3377,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr"/>
